--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.12723134878291</v>
+        <v>9.283175094177222</v>
       </c>
       <c r="D2" t="n">
-        <v>56.98372635515626</v>
+        <v>9.259855532712892</v>
       </c>
       <c r="E2" t="n">
-        <v>16.51616863831275</v>
+        <v>2.683877403725821</v>
       </c>
       <c r="F2" t="n">
-        <v>11.24879484496358</v>
+        <v>1.827929162306583</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.47468330982904</v>
+        <v>4.302136037847219</v>
       </c>
       <c r="D3" t="n">
-        <v>26.53956056593605</v>
+        <v>4.312678591964608</v>
       </c>
       <c r="E3" t="n">
-        <v>16.51616863831275</v>
+        <v>2.683877403725821</v>
       </c>
       <c r="F3" t="n">
-        <v>11.24879484496358</v>
+        <v>1.827929162306583</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.43280203428782</v>
+        <v>1.85783033057177</v>
       </c>
       <c r="D4" t="n">
-        <v>27.04553240002078</v>
+        <v>4.394899015003377</v>
       </c>
       <c r="E4" t="n">
-        <v>16.51616863831275</v>
+        <v>2.683877403725821</v>
       </c>
       <c r="F4" t="n">
-        <v>11.24879484496358</v>
+        <v>1.827929162306583</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.7650190887139</v>
+        <v>2.074315601916009</v>
       </c>
       <c r="D5" t="n">
-        <v>40.35824757462103</v>
+        <v>6.558215230875918</v>
       </c>
       <c r="E5" t="n">
-        <v>16.51616863831275</v>
+        <v>2.683877403725821</v>
       </c>
       <c r="F5" t="n">
-        <v>11.24879484496358</v>
+        <v>1.827929162306583</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.95897315376743</v>
+        <v>3.893333137487207</v>
       </c>
       <c r="D6" t="n">
-        <v>31.14634700358665</v>
+        <v>5.061281388082831</v>
       </c>
       <c r="E6" t="n">
-        <v>16.51616863831275</v>
+        <v>2.683877403725821</v>
       </c>
       <c r="F6" t="n">
-        <v>11.24879484496358</v>
+        <v>1.827929162306583</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.97932386250106</v>
+        <v>1.784140127656422</v>
       </c>
       <c r="D7" t="n">
-        <v>34.57137644290352</v>
+        <v>5.617848671971823</v>
       </c>
       <c r="E7" t="n">
-        <v>16.51616863831275</v>
+        <v>2.683877403725821</v>
       </c>
       <c r="F7" t="n">
-        <v>11.24879484496358</v>
+        <v>1.827929162306583</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.26459428707222</v>
+        <v>3.617996571649237</v>
       </c>
       <c r="D8" t="n">
-        <v>25.74969928586987</v>
+        <v>4.184326133953854</v>
       </c>
       <c r="E8" t="n">
-        <v>16.51616863831275</v>
+        <v>2.683877403725821</v>
       </c>
       <c r="F8" t="n">
-        <v>11.24879484496358</v>
+        <v>1.827929162306583</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.26168374962187</v>
+        <v>8.167523609313553</v>
       </c>
       <c r="D9" t="n">
-        <v>52.05691718821863</v>
+        <v>8.459249043085528</v>
       </c>
       <c r="E9" t="n">
-        <v>16.51616863831275</v>
+        <v>2.683877403725821</v>
       </c>
       <c r="F9" t="n">
-        <v>11.24879484496358</v>
+        <v>1.827929162306583</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
